--- a/www/flightdata/xlsx/eoss-303.xlsx
+++ b/www/flightdata/xlsx/eoss-303.xlsx
@@ -4578,7 +4578,7 @@
         <v>30593.39</v>
       </c>
       <c r="I2">
-        <v>894</v>
+        <v>626</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
